--- a/timings/eval.xlsx
+++ b/timings/eval.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixlinker/git/variant-restrictions/timings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8B27A4-6FEC-1E4A-91B6-19179AF027F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E5ACDB-8350-B34A-9148-6F0EFC52E520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4300" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{3DB891B5-6F67-014B-8918-C3F2D8F1EF1C}"/>
+    <workbookView xWindow="-4540" yWindow="-20980" windowWidth="33720" windowHeight="20980" activeTab="2" xr2:uid="{3DB891B5-6F67-014B-8918-C3F2D8F1EF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -23,12 +23,10 @@
     <definedName name="_xlchart.v1.1" hidden="1">prove!$D$2:$D$20</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">prove!$E$1</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">prove!$E$2:$E$20</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">prove!$D$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">prove!$D$2:$D$20</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">precomp!$E$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">precomp!$E$2:$E$20</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">precomp!$D$1</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">precomp!$D$2:$D$20</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">precomp!$E$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">precomp!$E$2:$E$20</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">precomp!$D$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">precomp!$D$2:$D$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -174,8 +172,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -214,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -225,12 +224,37 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -251,28 +275,10 @@
       <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -312,7 +318,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr algn="ctr" rtl="0">
-                  <a:defRPr sz="900" b="0" i="0">
+                  <a:defRPr sz="1400" b="0" i="0">
                     <a:solidFill>
                       <a:srgbClr val="404040"/>
                     </a:solidFill>
@@ -321,7 +327,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US">
+                <a:endParaRPr lang="en-US" sz="1400">
                   <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:endParaRPr>
@@ -395,7 +401,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -405,7 +411,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{6AF84F9E-4D9A-484B-8A7A-D775C77494EC}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Speedup Absolute</cx:v>
             </cx:txData>
           </cx:tx>
@@ -415,7 +421,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr algn="ctr" rtl="0">
-                  <a:defRPr sz="900" b="0" i="0">
+                  <a:defRPr sz="1400" b="0" i="0">
                     <a:solidFill>
                       <a:srgbClr val="404040"/>
                     </a:solidFill>
@@ -424,13 +430,14 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US">
+                <a:endParaRPr lang="en-US" sz="1400">
                   <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:endParaRPr>
               </a:p>
             </cx:txPr>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
+            <cx:dataLabelHidden idx="4"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
           <cx:layoutPr>
@@ -498,7 +505,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -508,7 +515,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{CC4050E1-099E-B34B-BA45-73A49BC9BC22}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.6</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Speedup Relative</cx:v>
             </cx:txData>
           </cx:tx>
@@ -518,7 +525,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr algn="ctr" rtl="0">
-                  <a:defRPr sz="900" b="0" i="0">
+                  <a:defRPr sz="1400" b="0" i="0">
                     <a:solidFill>
                       <a:srgbClr val="404040"/>
                     </a:solidFill>
@@ -527,7 +534,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US">
+                <a:endParaRPr lang="en-US" sz="1400">
                   <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:endParaRPr>
@@ -601,7 +608,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -611,7 +618,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{9B7B0826-150D-6C46-A5A9-3040F4C0EAEA}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Speedup Absolute</cx:v>
             </cx:txData>
           </cx:tx>
@@ -621,7 +628,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr algn="ctr" rtl="0">
-                  <a:defRPr sz="900" b="0" i="0">
+                  <a:defRPr sz="1400" b="0" i="0">
                     <a:solidFill>
                       <a:srgbClr val="404040"/>
                     </a:solidFill>
@@ -630,13 +637,18 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US">
+                <a:endParaRPr lang="en-US" sz="1400">
                   <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:endParaRPr>
               </a:p>
             </cx:txPr>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
+            <cx:dataLabelHidden idx="3"/>
+            <cx:dataLabelHidden idx="17"/>
+            <cx:dataLabelHidden idx="19"/>
+            <cx:dataLabelHidden idx="20"/>
+            <cx:dataLabelHidden idx="21"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
           <cx:layoutPr>
@@ -2874,9 +2886,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>804794</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>8006</xdr:rowOff>
+      <xdr:colOff>344833</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>160406</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2913,7 +2925,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="8091833" y="109606"/>
-              <a:ext cx="2745961" cy="4572000"/>
+              <a:ext cx="2286000" cy="4114800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2951,10 +2963,10 @@
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2991,7 +3003,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="5257800" y="120650"/>
-              <a:ext cx="2743200" cy="4572000"/>
+              <a:ext cx="2286000" cy="4114800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3035,9 +3047,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:colOff>192129</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123363</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -3074,7 +3086,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="11137900" y="336550"/>
-              <a:ext cx="2743200" cy="4572000"/>
+              <a:ext cx="2287629" cy="4054013"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3112,10 +3124,10 @@
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>506915</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>148763</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -3152,7 +3164,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="8153400" y="361950"/>
-              <a:ext cx="2743200" cy="4572000"/>
+              <a:ext cx="2284915" cy="4054013"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7163,15 +7175,18 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F5FC8E-D0FD-8A49-8498-7968C42044B1}" name="Table1" displayName="Table1" ref="A1:E21" totalsRowCount="1">
   <autoFilter ref="A1:E20" xr:uid="{B1F5FC8E-D0FD-8A49-8498-7968C42044B1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
+    <sortCondition ref="D1:D20"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B0C7120F-4C7F-1643-8D58-6FA251E0BD8E}" name="Theory" totalsRowLabel="Total"/>
-    <tableColumn id="3" xr3:uid="{15CF9D06-D850-4149-A8EC-50A9E0C43DCD}" name="Old" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{54D1268D-5C52-904F-9B56-6442067CDA55}" name="New" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{A674F842-A2F8-4342-903D-2B0D11AC1458}" name="Speedup Absolute" dataDxfId="6">
-      <calculatedColumnFormula>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{15CF9D06-D850-4149-A8EC-50A9E0C43DCD}" name="Old" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{54D1268D-5C52-904F-9B56-6442067CDA55}" name="New" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{A674F842-A2F8-4342-903D-2B0D11AC1458}" name="Speedup Absolute" dataDxfId="1">
+      <calculatedColumnFormula>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{54DA73FB-0436-BC4F-B96F-E616171F2B17}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Percent">
-      <calculatedColumnFormula>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{54DA73FB-0436-BC4F-B96F-E616171F2B17}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="5" dataCellStyle="Percent">
+      <calculatedColumnFormula>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1,Table1[Speedup Relative])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -7182,15 +7197,18 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FE5FCCD7-356A-364E-B70A-2FF85D8F7228}" name="Table2" displayName="Table2" ref="A1:E21" totalsRowCount="1">
   <autoFilter ref="A1:E20" xr:uid="{FE5FCCD7-356A-364E-B70A-2FF85D8F7228}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
+    <sortCondition ref="D1:D20"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{62380829-4076-B641-B74D-C168DDBA99F3}" name="Theory" totalsRowLabel="Total"/>
-    <tableColumn id="3" xr3:uid="{43DB2F9D-E8BC-2148-BE3C-2746441702FE}" name="Old"/>
-    <tableColumn id="4" xr3:uid="{C4E27E5A-C459-9E4D-B6CC-9B45E9E502C2}" name="New"/>
-    <tableColumn id="5" xr3:uid="{70F424DE-DFF6-B748-858B-2C3F776F1D05}" name="Speedup Absolute" dataDxfId="2">
-      <calculatedColumnFormula>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{43DB2F9D-E8BC-2148-BE3C-2746441702FE}" name="Old" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{C4E27E5A-C459-9E4D-B6CC-9B45E9E502C2}" name="New" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{70F424DE-DFF6-B748-858B-2C3F776F1D05}" name="Speedup Absolute" dataDxfId="3">
+      <calculatedColumnFormula>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7BFF99AE-129A-644B-B283-CAE7CB5DD4A7}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Percent" totalsRowCellStyle="Percent">
-      <calculatedColumnFormula>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{7BFF99AE-129A-644B-B283-CAE7CB5DD4A7}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="0" totalsRowDxfId="8" dataCellStyle="Percent" totalsRowCellStyle="Percent">
+      <calculatedColumnFormula>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1,Table2[Speedup Relative])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -7210,7 +7228,7 @@
     <tableColumn id="1" xr3:uid="{A6009477-5414-1846-8AA8-C63C0FB49A39}" name="Theory"/>
     <tableColumn id="2" xr3:uid="{DA754493-9B01-5E4C-93A0-B883AE6D6158}" name="User"/>
     <tableColumn id="3" xr3:uid="{C68678B9-4154-9E4B-8A14-CE222DB15C00}" name="Sys"/>
-    <tableColumn id="7" xr3:uid="{26B1A19C-B95B-0D40-812E-1ACF40858C87}" name="Sum" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{26B1A19C-B95B-0D40-812E-1ACF40858C87}" name="Sum" dataDxfId="4">
       <calculatedColumnFormula>Table3[[#This Row],[User]]+Table3[[#This Row],[Sys]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8418,361 +8436,361 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="6">
         <v>578.08000000000004</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>400.93</v>
       </c>
-      <c r="D2">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>177.15000000000003</v>
+      <c r="D2" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-177.15000000000003</v>
       </c>
       <c r="E2" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.30644547467478556</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.69355452532521444</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>436.60999999999996</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>325.94</v>
       </c>
-      <c r="D3">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>110.66999999999996</v>
+      <c r="D3" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-110.66999999999996</v>
       </c>
       <c r="E3" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.25347564187719007</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.74652435812280993</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>15.44</v>
-      </c>
-      <c r="C4">
-        <v>13.030000000000003</v>
-      </c>
-      <c r="D4">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>2.4099999999999966</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="6">
+        <v>302.67</v>
+      </c>
+      <c r="C4" s="6">
+        <v>249.39</v>
+      </c>
+      <c r="D4" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-53.28000000000003</v>
       </c>
       <c r="E4" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.15608808290155418</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.82396669640202191</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>15.819999999999999</v>
-      </c>
-      <c r="C5">
-        <v>12.81</v>
-      </c>
-      <c r="D5">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>3.009999999999998</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="6">
+        <v>203.88</v>
+      </c>
+      <c r="C5" s="6">
+        <v>158</v>
+      </c>
+      <c r="D5" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-45.879999999999995</v>
       </c>
       <c r="E5" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.19026548672566357</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.77496566607808515</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>15.36</v>
-      </c>
-      <c r="C6">
-        <v>15.29</v>
-      </c>
-      <c r="D6">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>7.0000000000000284E-2</v>
+        <v>28</v>
+      </c>
+      <c r="B6" s="6">
+        <v>111.55000000000001</v>
+      </c>
+      <c r="C6" s="6">
+        <v>100.69</v>
+      </c>
+      <c r="D6" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-10.860000000000014</v>
       </c>
       <c r="E6" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>4.5572916666667407E-3</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.90264455401165389</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>9.26</v>
-      </c>
-      <c r="C7">
-        <v>9.26</v>
-      </c>
-      <c r="D7">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>57.77</v>
+      </c>
+      <c r="C7" s="6">
+        <v>50.86</v>
+      </c>
+      <c r="D7" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-6.9100000000000037</v>
       </c>
       <c r="E7" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.88038774450406776</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>193.42000000000002</v>
-      </c>
-      <c r="C8">
-        <v>204.23000000000002</v>
-      </c>
-      <c r="D8">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>-10.810000000000002</v>
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
+        <v>59.900000000000006</v>
+      </c>
+      <c r="C8" s="6">
+        <v>53.6</v>
+      </c>
+      <c r="D8" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-6.3000000000000043</v>
       </c>
       <c r="E8" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>-5.5888739530555176E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.89482470784641066</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>130.44999999999999</v>
-      </c>
-      <c r="C9">
-        <v>125.52000000000001</v>
-      </c>
-      <c r="D9">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>4.9299999999999784</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="6">
+        <v>107.99000000000001</v>
+      </c>
+      <c r="C9" s="6">
+        <v>102.59999999999998</v>
+      </c>
+      <c r="D9" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-5.390000000000029</v>
       </c>
       <c r="E9" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>3.7792257569949972E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.95008797110843568</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>580.04</v>
-      </c>
-      <c r="C10">
-        <v>589.52</v>
-      </c>
-      <c r="D10">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>-9.4800000000000182</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="C10" s="6">
+        <v>125.52000000000001</v>
+      </c>
+      <c r="D10" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-4.9299999999999784</v>
       </c>
       <c r="E10" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>-1.6343700434452879E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.96220774243005003</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11">
-        <v>302.67</v>
-      </c>
-      <c r="C11">
-        <v>249.39</v>
-      </c>
-      <c r="D11">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>53.28000000000003</v>
+        <v>2</v>
+      </c>
+      <c r="B11" s="6">
+        <v>15.819999999999999</v>
+      </c>
+      <c r="C11" s="6">
+        <v>12.81</v>
+      </c>
+      <c r="D11" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-3.009999999999998</v>
       </c>
       <c r="E11" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.17603330359797809</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.80973451327433643</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12">
-        <v>203.88</v>
-      </c>
-      <c r="C12">
-        <v>158</v>
-      </c>
-      <c r="D12">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>45.879999999999995</v>
+        <v>3</v>
+      </c>
+      <c r="B12" s="6">
+        <v>15.44</v>
+      </c>
+      <c r="C12" s="6">
+        <v>13.030000000000003</v>
+      </c>
+      <c r="D12" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-2.4099999999999966</v>
       </c>
       <c r="E12" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.22503433392191485</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.84391191709844582</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13">
-        <v>74.390000000000015</v>
-      </c>
-      <c r="C13">
-        <v>76.28</v>
-      </c>
-      <c r="D13">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>-1.8899999999999864</v>
+        <v>4</v>
+      </c>
+      <c r="B13" s="6">
+        <v>15.36</v>
+      </c>
+      <c r="C13" s="6">
+        <v>15.29</v>
+      </c>
+      <c r="D13" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>-7.0000000000000284E-2</v>
       </c>
       <c r="E13" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>-2.5406640677510195E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>0.99544270833333326</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14">
-        <v>93.359999999999985</v>
-      </c>
-      <c r="C14">
-        <v>98.210000000000008</v>
-      </c>
-      <c r="D14">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>-4.8500000000000227</v>
+        <v>5</v>
+      </c>
+      <c r="B14" s="6">
+        <v>9.26</v>
+      </c>
+      <c r="C14" s="6">
+        <v>9.26</v>
+      </c>
+      <c r="D14" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>0</v>
       </c>
       <c r="E14" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>-5.1949443016281238E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>59.900000000000006</v>
-      </c>
-      <c r="C15">
-        <v>53.6</v>
-      </c>
-      <c r="D15">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>6.3000000000000043</v>
+        <v>24</v>
+      </c>
+      <c r="B15" s="6">
+        <v>74.390000000000015</v>
+      </c>
+      <c r="C15" s="6">
+        <v>76.28</v>
+      </c>
+      <c r="D15" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>1.8899999999999864</v>
       </c>
       <c r="E15" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.10517529215358934</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1.0254066406775102</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16">
-        <v>57.77</v>
-      </c>
-      <c r="C16">
-        <v>50.86</v>
-      </c>
-      <c r="D16">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>6.9100000000000037</v>
+        <v>25</v>
+      </c>
+      <c r="B16" s="6">
+        <v>93.359999999999985</v>
+      </c>
+      <c r="C16" s="6">
+        <v>98.210000000000008</v>
+      </c>
+      <c r="D16" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>4.8500000000000227</v>
       </c>
       <c r="E16" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>0.11961225549593224</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1.0519494430162812</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17">
-        <v>111.55000000000001</v>
-      </c>
-      <c r="C17">
-        <v>100.69</v>
-      </c>
-      <c r="D17">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>10.860000000000014</v>
+        <v>31</v>
+      </c>
+      <c r="B17" s="6">
+        <v>247.90000000000003</v>
+      </c>
+      <c r="C17" s="6">
+        <v>254.74</v>
+      </c>
+      <c r="D17" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>6.839999999999975</v>
       </c>
       <c r="E17" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>9.7355445988346112E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1.0275917708753528</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18">
-        <v>107.99000000000001</v>
-      </c>
-      <c r="C18">
-        <v>102.59999999999998</v>
-      </c>
-      <c r="D18">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>5.390000000000029</v>
+        <v>30</v>
+      </c>
+      <c r="B18" s="6">
+        <v>164.06</v>
+      </c>
+      <c r="C18" s="6">
+        <v>171.64000000000001</v>
+      </c>
+      <c r="D18" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>7.5800000000000125</v>
       </c>
       <c r="E18" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>4.991202889156432E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1.0462026088016581</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19">
-        <v>164.06</v>
-      </c>
-      <c r="C19">
-        <v>171.64000000000001</v>
-      </c>
-      <c r="D19">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>-7.5800000000000125</v>
+        <v>6</v>
+      </c>
+      <c r="B19" s="6">
+        <v>580.04</v>
+      </c>
+      <c r="C19" s="6">
+        <v>589.52</v>
+      </c>
+      <c r="D19" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>9.4800000000000182</v>
       </c>
       <c r="E19" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>-4.6202608801658052E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1.0163437004344529</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20">
-        <v>247.90000000000003</v>
-      </c>
-      <c r="C20">
-        <v>254.74</v>
-      </c>
-      <c r="D20">
-        <f>Table1[[#This Row],[Old]]-Table1[[#This Row],[New]]</f>
-        <v>-6.839999999999975</v>
+        <v>8</v>
+      </c>
+      <c r="B20" s="6">
+        <v>193.42000000000002</v>
+      </c>
+      <c r="C20" s="6">
+        <v>204.23000000000002</v>
+      </c>
+      <c r="D20" s="6">
+        <f>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</f>
+        <v>10.810000000000002</v>
       </c>
       <c r="E20" s="4">
-        <f>(1-Table1[[#This Row],[New]]/Table1[[#This Row],[Old]])</f>
-        <v>-2.7591770875352806E-2</v>
+        <f>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</f>
+        <v>1.0558887395305552</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -8781,7 +8799,7 @@
       </c>
       <c r="E21" s="5">
         <f>SUBTOTAL(1,Table1[Speedup Relative])</f>
-        <v>7.8861262743648686E-2</v>
+        <v>0.92113873725635143</v>
       </c>
     </row>
   </sheetData>
@@ -8824,361 +8842,361 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="6">
         <v>113.86</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>36.32</v>
       </c>
-      <c r="D2">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>77.539999999999992</v>
+      <c r="D2" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-77.539999999999992</v>
       </c>
       <c r="E2" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.681011768838925</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.318988231161075</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>113.31</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>36.089999999999996</v>
       </c>
-      <c r="D3">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>77.22</v>
+      <c r="D3" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-77.22</v>
       </c>
       <c r="E3" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.68149324861000804</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.31850675138999202</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1.98</v>
-      </c>
-      <c r="C4">
-        <v>1.27</v>
-      </c>
-      <c r="D4">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.71</v>
+        <v>25</v>
+      </c>
+      <c r="B4" s="6">
+        <v>23.74</v>
+      </c>
+      <c r="C4" s="6">
+        <v>19.39</v>
+      </c>
+      <c r="D4" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-4.3499999999999979</v>
       </c>
       <c r="E4" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.35858585858585856</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.81676495366470103</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1.9600000000000002</v>
-      </c>
-      <c r="C5">
-        <v>1.29</v>
-      </c>
-      <c r="D5">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.67000000000000015</v>
+        <v>22</v>
+      </c>
+      <c r="B5" s="6">
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="D5" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-1.2799999999999994</v>
       </c>
       <c r="E5" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.34183673469387754</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.58709677419354855</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>0.61</v>
-      </c>
-      <c r="C6">
-        <v>0.6</v>
-      </c>
-      <c r="D6">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>1.0000000000000009E-2</v>
+        <v>23</v>
+      </c>
+      <c r="B6" s="6">
+        <v>3.0500000000000003</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1.8100000000000003</v>
+      </c>
+      <c r="D6" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-1.24</v>
       </c>
       <c r="E6" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>1.6393442622950838E-2</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.59344262295081973</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0.62</v>
-      </c>
-      <c r="C7">
-        <v>0.6</v>
-      </c>
-      <c r="D7">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>2.0000000000000018E-2</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1.98</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.27</v>
+      </c>
+      <c r="D7" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.71</v>
       </c>
       <c r="E7" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>3.2258064516129115E-2</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.64141414141414144</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>1.9400000000000002</v>
-      </c>
-      <c r="C8">
-        <v>1.7500000000000002</v>
-      </c>
-      <c r="D8">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.18999999999999995</v>
+        <v>2</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1.9600000000000002</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="D8" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.67000000000000015</v>
       </c>
       <c r="E8" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>9.7938144329896892E-2</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.65816326530612246</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>2.44</v>
-      </c>
-      <c r="C9">
-        <v>2.23</v>
-      </c>
-      <c r="D9">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.20999999999999996</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.5</v>
       </c>
       <c r="E9" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>8.6065573770491843E-2</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.73118279569892475</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>1.8599999999999999</v>
-      </c>
-      <c r="C10">
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="D10">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.5</v>
+        <v>27</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="D10" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.31999999999999984</v>
       </c>
       <c r="E10" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.26881720430107525</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.71929824561403521</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11">
-        <v>3.0999999999999996</v>
-      </c>
-      <c r="C11">
-        <v>1.8200000000000003</v>
-      </c>
-      <c r="D11">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>1.2799999999999994</v>
+        <v>26</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1.1099999999999999</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="D11" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.28999999999999981</v>
       </c>
       <c r="E11" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.41290322580645145</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.73873873873873885</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12">
-        <v>3.0500000000000003</v>
-      </c>
-      <c r="C12">
-        <v>1.8100000000000003</v>
-      </c>
-      <c r="D12">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>1.24</v>
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>2.44</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="D12" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.20999999999999996</v>
       </c>
       <c r="E12" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.40655737704918027</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.91393442622950816</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13">
-        <v>19.510000000000002</v>
-      </c>
-      <c r="C13">
-        <v>28.16</v>
-      </c>
-      <c r="D13">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>-8.6499999999999986</v>
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1.9400000000000002</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.7500000000000002</v>
+      </c>
+      <c r="D13" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.18999999999999995</v>
       </c>
       <c r="E13" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>-0.44336237826755509</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.90206185567010311</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14">
-        <v>23.74</v>
-      </c>
-      <c r="C14">
-        <v>19.39</v>
-      </c>
-      <c r="D14">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>4.3499999999999979</v>
+        <v>28</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="D14" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.10999999999999999</v>
       </c>
       <c r="E14" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.18323504633529897</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.83582089552238803</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>1.1099999999999999</v>
-      </c>
-      <c r="C15">
-        <v>0.82000000000000006</v>
-      </c>
-      <c r="D15">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.28999999999999981</v>
+        <v>29</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D15" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-0.10999999999999999</v>
       </c>
       <c r="E15" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.26126126126126115</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.84507042253521125</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C16">
-        <v>0.82000000000000006</v>
-      </c>
-      <c r="D16">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.31999999999999984</v>
+        <v>30</v>
+      </c>
+      <c r="B16" s="6">
+        <v>2.2500000000000004</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2.1900000000000004</v>
+      </c>
+      <c r="D16" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-6.0000000000000053E-2</v>
       </c>
       <c r="E16" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.28070175438596479</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.97333333333333327</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17">
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="C17">
-        <v>0.55999999999999994</v>
-      </c>
-      <c r="D17">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.10999999999999999</v>
+        <v>5</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.62</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D17" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="E17" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.16417910447761197</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.96774193548387089</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18">
-        <v>0.71</v>
-      </c>
-      <c r="C18">
-        <v>0.6</v>
-      </c>
-      <c r="D18">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>0.10999999999999999</v>
+        <v>31</v>
+      </c>
+      <c r="B18" s="6">
+        <v>2.2500000000000004</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="D18" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-1.0000000000000231E-2</v>
       </c>
       <c r="E18" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>0.15492957746478875</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.99555555555555542</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19">
-        <v>2.2500000000000004</v>
-      </c>
-      <c r="C19">
-        <v>2.1900000000000004</v>
-      </c>
-      <c r="D19">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>6.0000000000000053E-2</v>
+        <v>4</v>
+      </c>
+      <c r="B19" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D19" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="E19" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>2.6666666666666727E-2</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>0.98360655737704916</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20">
-        <v>2.2500000000000004</v>
-      </c>
-      <c r="C20">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="D20">
-        <f>Table2[[#This Row],[Old]]-Table2[[#This Row],[New]]</f>
-        <v>1.0000000000000231E-2</v>
+        <v>24</v>
+      </c>
+      <c r="B20" s="6">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="C20" s="6">
+        <v>28.16</v>
+      </c>
+      <c r="D20" s="6">
+        <f>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</f>
+        <v>8.6499999999999986</v>
       </c>
       <c r="E20" s="4">
-        <f>(1-Table2[[#This Row],[New]]/Table2[[#This Row],[Old]])</f>
-        <v>4.4444444444445841E-3</v>
+        <f>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</f>
+        <v>1.4433623782675551</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -9187,7 +9205,7 @@
       </c>
       <c r="E21" s="4">
         <f>SUBTOTAL(1,Table2[Speedup Relative])</f>
-        <v>0.21136400631017507</v>
+        <v>0.78863599368982484</v>
       </c>
     </row>
   </sheetData>

--- a/timings/eval.xlsx
+++ b/timings/eval.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felixlinker/git/variant-restrictions/timings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E5ACDB-8350-B34A-9148-6F0EFC52E520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A583210-932E-1B47-85E3-598A4142A5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4540" yWindow="-20980" windowWidth="33720" windowHeight="20980" activeTab="2" xr2:uid="{3DB891B5-6F67-014B-8918-C3F2D8F1EF1C}"/>
   </bookViews>
@@ -19,10 +19,10 @@
     <sheet name="results" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">prove!$D$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">prove!$D$2:$D$20</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">prove!$E$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">prove!$E$2:$E$20</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">prove!$E$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">prove!$E$2:$E$20</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">prove!$D$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">prove!$D$2:$D$20</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">precomp!$E$1</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">precomp!$E$2:$E$20</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">precomp!$D$1</definedName>
@@ -232,22 +232,16 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
@@ -275,6 +269,12 @@
       <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="0.00\ &quot;s&quot;"/>
     </dxf>
     <dxf>
@@ -298,7 +298,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -308,7 +308,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{E45AC5B5-D6F2-8A47-A0BE-15A0BBE64F69}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Speedup Relative</cx:v>
             </cx:txData>
           </cx:tx>
@@ -401,7 +401,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -411,7 +411,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{6AF84F9E-4D9A-484B-8A7A-D775C77494EC}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Speedup Absolute</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2887,8 +2887,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>344833</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>160406</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>109606</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2925,7 +2925,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="8091833" y="109606"/>
-              <a:ext cx="2286000" cy="4114800"/>
+              <a:ext cx="2286000" cy="3657600"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2965,8 +2965,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -3003,7 +3003,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="5257800" y="120650"/>
-              <a:ext cx="2286000" cy="4114800"/>
+              <a:ext cx="2286000" cy="3657600"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3048,8 +3048,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>192129</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123363</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>150717</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -3085,8 +3085,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11137900" y="336550"/>
-              <a:ext cx="2287629" cy="4054013"/>
+              <a:off x="11138009" y="339589"/>
+              <a:ext cx="2286000" cy="2286000"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3126,8 +3126,8 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>506915</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>148763</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>176117</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -3163,8 +3163,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8153400" y="361950"/>
-              <a:ext cx="2284915" cy="4054013"/>
+              <a:off x="8152966" y="364989"/>
+              <a:ext cx="2286000" cy="2286000"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7180,12 +7180,12 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B0C7120F-4C7F-1643-8D58-6FA251E0BD8E}" name="Theory" totalsRowLabel="Total"/>
-    <tableColumn id="3" xr3:uid="{15CF9D06-D850-4149-A8EC-50A9E0C43DCD}" name="Old" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{54D1268D-5C52-904F-9B56-6442067CDA55}" name="New" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{A674F842-A2F8-4342-903D-2B0D11AC1458}" name="Speedup Absolute" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{15CF9D06-D850-4149-A8EC-50A9E0C43DCD}" name="Old" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{54D1268D-5C52-904F-9B56-6442067CDA55}" name="New" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{A674F842-A2F8-4342-903D-2B0D11AC1458}" name="Speedup Absolute" dataDxfId="3">
       <calculatedColumnFormula>Table1[[#This Row],[New]]-Table1[[#This Row],[Old]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{54DA73FB-0436-BC4F-B96F-E616171F2B17}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="5" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{54DA73FB-0436-BC4F-B96F-E616171F2B17}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="1" dataCellStyle="Percent">
       <calculatedColumnFormula>Table1[[#This Row],[New]]/Table1[[#This Row],[Old]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1,Table1[Speedup Relative])</totalsRowFormula>
     </tableColumn>
@@ -7204,10 +7204,10 @@
     <tableColumn id="1" xr3:uid="{62380829-4076-B641-B74D-C168DDBA99F3}" name="Theory" totalsRowLabel="Total"/>
     <tableColumn id="3" xr3:uid="{43DB2F9D-E8BC-2148-BE3C-2746441702FE}" name="Old" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{C4E27E5A-C459-9E4D-B6CC-9B45E9E502C2}" name="New" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{70F424DE-DFF6-B748-858B-2C3F776F1D05}" name="Speedup Absolute" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{70F424DE-DFF6-B748-858B-2C3F776F1D05}" name="Speedup Absolute" dataDxfId="8">
       <calculatedColumnFormula>Table2[[#This Row],[New]]-Table2[[#This Row],[Old]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7BFF99AE-129A-644B-B283-CAE7CB5DD4A7}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="0" totalsRowDxfId="8" dataCellStyle="Percent" totalsRowCellStyle="Percent">
+    <tableColumn id="6" xr3:uid="{7BFF99AE-129A-644B-B283-CAE7CB5DD4A7}" name="Speedup Relative" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Percent" totalsRowCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[New]]/Table2[[#This Row],[Old]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1,Table2[Speedup Relative])</totalsRowFormula>
     </tableColumn>
@@ -7228,7 +7228,7 @@
     <tableColumn id="1" xr3:uid="{A6009477-5414-1846-8AA8-C63C0FB49A39}" name="Theory"/>
     <tableColumn id="2" xr3:uid="{DA754493-9B01-5E4C-93A0-B883AE6D6158}" name="User"/>
     <tableColumn id="3" xr3:uid="{C68678B9-4154-9E4B-8A14-CE222DB15C00}" name="Sys"/>
-    <tableColumn id="7" xr3:uid="{26B1A19C-B95B-0D40-812E-1ACF40858C87}" name="Sum" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{26B1A19C-B95B-0D40-812E-1ACF40858C87}" name="Sum" dataDxfId="0">
       <calculatedColumnFormula>Table3[[#This Row],[User]]+Table3[[#This Row],[Sys]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
